--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-medicationadministration.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-medicationadministration.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1616" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1616" uniqueCount="357">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-18T10:23:29+00:00</t>
+    <t>2026-01-28T10:05:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -511,7 +511,7 @@
     <t>MedicationAdministration.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|Procedure|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-medicationadministration|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-procedure)
 </t>
   </si>
   <si>
@@ -612,8 +612,8 @@
     <t>MedicationAdministration.medication[x]</t>
   </si>
   <si>
-    <t>CodeableConcept
-Reference(Medication|4.0.1)</t>
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-medication)
+</t>
   </si>
   <si>
     <t>What was administered</t>
@@ -623,12 +623,6 @@
   </si>
   <si>
     <t>If only a code is specified, then it needs to be a code for a specific product. If more information is required, then the use of the medication resource is recommended.  For example, if you require form or lot number, then you must reference the Medication resource.</t>
-  </si>
-  <si>
-    <t>Codes identifying substance or product that can be administered.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -828,7 +822,7 @@
     <t>MedicationAdministration.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Device|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|RelatedPerson|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-device)
 </t>
   </si>
   <si>
@@ -871,7 +865,7 @@
     <t>MedicationAdministration.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-condition|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-observation|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-diagnosticreport)
 </t>
   </si>
   <si>
@@ -899,7 +893,7 @@
     <t>MedicationAdministration.request</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-medicationrequest)
 </t>
   </si>
   <si>
@@ -924,7 +918,7 @@
     <t>MedicationAdministration.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-device)
 </t>
   </si>
   <si>
@@ -1450,7 +1444,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="78.85546875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="232.3671875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -3415,13 +3409,13 @@
         <v>79</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>180</v>
+        <v>79</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>198</v>
+        <v>79</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>79</v>
@@ -3454,16 +3448,16 @@
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>79</v>
@@ -3471,10 +3465,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3497,13 +3491,13 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3554,7 +3548,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>89</v>
@@ -3569,16 +3563,16 @@
         <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="AL18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>79</v>
@@ -3586,10 +3580,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3612,13 +3606,13 @@
         <v>79</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3669,7 +3663,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -3684,16 +3678,16 @@
         <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AL19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>79</v>
@@ -3701,10 +3695,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3727,13 +3721,13 @@
         <v>79</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3784,7 +3778,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3802,10 +3796,10 @@
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>79</v>
@@ -3816,10 +3810,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3842,13 +3836,13 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="L21" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3899,7 +3893,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>89</v>
@@ -3914,16 +3908,16 @@
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AL21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>79</v>
@@ -3931,10 +3925,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3957,13 +3951,13 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4014,7 +4008,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4029,16 +4023,16 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>79</v>
@@ -4046,10 +4040,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4072,13 +4066,13 @@
         <v>79</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4129,7 +4123,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4147,7 +4141,7 @@
         <v>79</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>79</v>
@@ -4161,10 +4155,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4193,7 +4187,7 @@
         <v>136</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>138</v>
@@ -4246,7 +4240,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4264,7 +4258,7 @@
         <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>79</v>
@@ -4278,14 +4272,14 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4307,10 +4301,10 @@
         <v>135</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>138</v>
@@ -4365,7 +4359,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4397,10 +4391,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4426,10 +4420,10 @@
         <v>177</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4459,10 +4453,10 @@
         <v>180</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>79</v>
@@ -4480,7 +4474,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4495,10 +4489,10 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>79</v>
@@ -4512,10 +4506,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4538,13 +4532,13 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4595,7 +4589,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>89</v>
@@ -4610,10 +4604,10 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>79</v>
@@ -4627,10 +4621,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4656,10 +4650,10 @@
         <v>177</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4689,10 +4683,10 @@
         <v>180</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>79</v>
@@ -4710,7 +4704,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4725,16 +4719,16 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>79</v>
@@ -4742,10 +4736,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4768,16 +4762,16 @@
         <v>79</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4827,7 +4821,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -4842,27 +4836,27 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO29" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>283</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4885,16 +4879,16 @@
         <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4944,7 +4938,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4959,16 +4953,16 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>79</v>
@@ -4976,10 +4970,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5002,13 +4996,13 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5059,7 +5053,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5077,13 +5071,13 @@
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>79</v>
@@ -5091,10 +5085,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5117,13 +5111,13 @@
         <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5174,7 +5168,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5189,10 +5183,10 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>79</v>
@@ -5206,10 +5200,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5232,13 +5226,13 @@
         <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5289,7 +5283,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5301,13 +5295,13 @@
         <v>79</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>79</v>
@@ -5321,10 +5315,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5347,13 +5341,13 @@
         <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="L34" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5404,7 +5398,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5422,7 +5416,7 @@
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>79</v>
@@ -5436,10 +5430,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5468,7 +5462,7 @@
         <v>136</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>138</v>
@@ -5521,7 +5515,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5539,7 +5533,7 @@
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>79</v>
@@ -5553,14 +5547,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5582,10 +5576,10 @@
         <v>135</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>138</v>
@@ -5640,7 +5634,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5672,10 +5666,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5698,13 +5692,13 @@
         <v>79</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5755,7 +5749,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5773,7 +5767,7 @@
         <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>79</v>
@@ -5787,10 +5781,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5816,13 +5810,13 @@
         <v>177</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="N38" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5851,10 +5845,10 @@
         <v>180</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>79</v>
@@ -5872,7 +5866,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5890,13 +5884,13 @@
         <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>79</v>
@@ -5904,10 +5898,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5933,10 +5927,10 @@
         <v>177</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5966,10 +5960,10 @@
         <v>180</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>79</v>
@@ -5987,7 +5981,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6005,13 +5999,13 @@
         <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>79</v>
@@ -6019,10 +6013,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6048,13 +6042,13 @@
         <v>177</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6083,10 +6077,10 @@
         <v>180</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
@@ -6104,7 +6098,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6122,13 +6116,13 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>79</v>
@@ -6136,10 +6130,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6162,16 +6156,16 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6221,7 +6215,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6239,13 +6233,13 @@
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>79</v>
@@ -6253,10 +6247,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6279,16 +6273,16 @@
         <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6338,7 +6332,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6356,13 +6350,13 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>79</v>
@@ -6370,10 +6364,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6396,16 +6390,16 @@
         <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6455,7 +6449,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6473,7 +6467,7 @@
         <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>79</v>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-medicationadministration.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-medicationadministration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T10:05:57+00:00</t>
+    <t>2026-01-29T06:33:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-medicationadministration.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-medicationadministration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T06:33:09+00:00</t>
+    <t>2026-02-03T10:06:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-medicationadministration.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-medicationadministration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T10:06:44+00:00</t>
+    <t>2026-02-03T10:34:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-medicationadministration.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-medicationadministration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T10:34:36+00:00</t>
+    <t>2026-02-09T07:50:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-medicationadministration.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-medicationadministration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T07:50:08+00:00</t>
+    <t>2026-02-13T12:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-medicationadministration.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-medicationadministration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T12:44:21+00:00</t>
+    <t>2026-02-16T08:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-medicationadministration.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-medicationadministration.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T08:31:54+00:00</t>
+    <t>2026-02-16T11:13:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-medicationadministration.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-medicationadministration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T11:13:42+00:00</t>
+    <t>2026-02-17T09:00:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-medicationadministration.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-medicationadministration.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T09:00:43+00:00</t>
+    <t>2026-09-01T07:40:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
